--- a/Wheat.xlsx
+++ b/Wheat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adm-my.sharepoint.com/personal/zeina_sherif_adm-medsofts_com/Documents/Documents/Commodity/Wheat/Local/Model Monthly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="11_AD4D80C4656A4B7AC02E743F331E4E205ADEDD8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02F873BC-B999-4A56-BA3B-FF208E33C4C4}"/>
+  <xr:revisionPtr revIDLastSave="449" documentId="11_AD4D80C4656A4B7AC02E743F331E4E205ADEDD8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7B3BEB-1D5A-4803-B5EC-600F9DDEE3B5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2380" yWindow="2810" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SnD" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
     <numFmt numFmtId="165" formatCode="[$EGP]\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="[$EGP]\ #,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,6 +114,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -210,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -260,6 +268,24 @@
     <xf numFmtId="17" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -282,6 +308,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -553,7 +583,7 @@
     <col min="1" max="1" width="9.90625" style="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="24" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -636,19 +666,19 @@
         <v>140000</v>
       </c>
       <c r="G2" s="13">
-        <f t="shared" ref="G2:G22" si="0">E2+F2</f>
+        <f>E2+F2</f>
         <v>780000</v>
       </c>
       <c r="H2" s="13">
-        <v>433000</v>
+        <v>434000</v>
       </c>
       <c r="I2" s="13">
-        <f t="shared" ref="I2:I22" si="1">G2-H2</f>
-        <v>347000</v>
+        <f t="shared" ref="I2:I42" si="0">G2-H2</f>
+        <v>346000</v>
       </c>
       <c r="J2" s="14">
         <f>I2/H2</f>
-        <v>0.80138568129330257</v>
+        <v>0.79723502304147464</v>
       </c>
       <c r="K2" s="15">
         <v>11830</v>
@@ -682,26 +712,26 @@
         <v>30.474</v>
       </c>
       <c r="E3" s="13">
-        <f t="shared" ref="E3:E13" si="2">I2</f>
-        <v>347000</v>
+        <f t="shared" ref="E3:E7" si="1">I2</f>
+        <v>346000</v>
       </c>
       <c r="F3" s="13">
         <v>430000</v>
       </c>
       <c r="G3" s="13">
-        <f t="shared" si="0"/>
-        <v>777000</v>
+        <f t="shared" ref="G3:G22" si="2">E3+F3</f>
+        <v>776000</v>
       </c>
       <c r="H3" s="13">
         <v>457000</v>
       </c>
       <c r="I3" s="13">
-        <f t="shared" si="1"/>
-        <v>320000</v>
+        <f t="shared" si="0"/>
+        <v>319000</v>
       </c>
       <c r="J3" s="14">
-        <f t="shared" ref="J3:J39" si="3">I3/H3</f>
-        <v>0.70021881838074396</v>
+        <f t="shared" ref="J3:J42" si="3">I3/H3</f>
+        <v>0.69803063457330417</v>
       </c>
       <c r="K3" s="15">
         <v>12150</v>
@@ -735,26 +765,26 @@
         <v>30.834</v>
       </c>
       <c r="E4" s="13">
-        <f t="shared" si="2"/>
-        <v>320000</v>
+        <f t="shared" si="1"/>
+        <v>319000</v>
       </c>
       <c r="F4" s="13">
         <v>620000</v>
       </c>
       <c r="G4" s="13">
-        <f t="shared" si="0"/>
-        <v>940000</v>
+        <f t="shared" si="2"/>
+        <v>939000</v>
       </c>
       <c r="H4" s="13">
         <v>494000</v>
       </c>
       <c r="I4" s="13">
-        <f t="shared" si="1"/>
-        <v>446000</v>
+        <f t="shared" si="0"/>
+        <v>445000</v>
       </c>
       <c r="J4" s="14">
         <f t="shared" si="3"/>
-        <v>0.90283400809716596</v>
+        <v>0.90080971659919029</v>
       </c>
       <c r="K4" s="15">
         <v>13050</v>
@@ -788,26 +818,26 @@
         <v>30.864999999999998</v>
       </c>
       <c r="E5" s="13">
-        <f t="shared" si="2"/>
-        <v>446000</v>
+        <f t="shared" si="1"/>
+        <v>445000</v>
       </c>
       <c r="F5" s="13">
         <v>465000</v>
       </c>
       <c r="G5" s="13">
-        <f t="shared" si="0"/>
-        <v>911000</v>
+        <f t="shared" si="2"/>
+        <v>910000</v>
       </c>
       <c r="H5" s="13">
         <v>494000</v>
       </c>
       <c r="I5" s="13">
-        <f t="shared" si="1"/>
-        <v>417000</v>
+        <f t="shared" si="0"/>
+        <v>416000</v>
       </c>
       <c r="J5" s="14">
         <f t="shared" si="3"/>
-        <v>0.84412955465587047</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="K5" s="15">
         <v>13050</v>
@@ -841,26 +871,26 @@
         <v>30.881</v>
       </c>
       <c r="E6" s="13">
-        <f t="shared" si="2"/>
-        <v>417000</v>
+        <f t="shared" si="1"/>
+        <v>416000</v>
       </c>
       <c r="F6" s="13">
         <v>565000</v>
       </c>
       <c r="G6" s="13">
-        <f t="shared" si="0"/>
-        <v>982000</v>
+        <f t="shared" si="2"/>
+        <v>981000</v>
       </c>
       <c r="H6" s="13">
         <v>494000</v>
       </c>
       <c r="I6" s="13">
-        <f t="shared" si="1"/>
-        <v>488000</v>
+        <f t="shared" si="0"/>
+        <v>487000</v>
       </c>
       <c r="J6" s="14">
         <f t="shared" si="3"/>
-        <v>0.98785425101214575</v>
+        <v>0.98582995951417007</v>
       </c>
       <c r="K6" s="15">
         <v>12700</v>
@@ -880,55 +910,55 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="22">
+    <row r="7" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="25">
         <v>45078</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="26">
         <v>352</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="27">
         <v>660</v>
       </c>
       <c r="D7" s="24">
         <v>30.895</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="28">
+        <f t="shared" si="1"/>
+        <v>487000</v>
+      </c>
+      <c r="F7" s="28">
+        <v>520000</v>
+      </c>
+      <c r="G7" s="28">
         <f t="shared" si="2"/>
-        <v>488000</v>
-      </c>
-      <c r="F7" s="13">
-        <v>520000</v>
-      </c>
-      <c r="G7" s="13">
-        <f t="shared" si="0"/>
-        <v>1008000</v>
-      </c>
-      <c r="H7" s="13">
+        <v>1007000</v>
+      </c>
+      <c r="H7" s="28">
         <v>619000</v>
       </c>
       <c r="I7" s="13">
-        <f t="shared" si="1"/>
-        <v>389000</v>
-      </c>
-      <c r="J7" s="14">
-        <f t="shared" si="3"/>
-        <v>0.62843295638126007</v>
-      </c>
-      <c r="K7" s="15">
+        <f t="shared" si="0"/>
+        <v>388000</v>
+      </c>
+      <c r="J7" s="29">
+        <f t="shared" si="3"/>
+        <v>0.62681744749596124</v>
+      </c>
+      <c r="K7" s="30">
         <v>12450</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="31">
         <v>257.5</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="30">
         <v>12500</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="31">
         <v>262.5</v>
       </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="2">
+      <c r="O7" s="32"/>
+      <c r="P7" s="33">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
@@ -947,26 +977,26 @@
         <v>30.882999999999999</v>
       </c>
       <c r="E8" s="13">
-        <f t="shared" si="2"/>
-        <v>389000</v>
+        <f>I7</f>
+        <v>388000</v>
       </c>
       <c r="F8" s="13">
         <v>370000</v>
       </c>
       <c r="G8" s="13">
-        <f t="shared" si="0"/>
-        <v>759000</v>
+        <f>E8+F8</f>
+        <v>758000</v>
       </c>
       <c r="H8" s="13">
         <v>619000</v>
       </c>
       <c r="I8" s="13">
-        <f t="shared" si="1"/>
-        <v>140000</v>
+        <f t="shared" si="0"/>
+        <v>139000</v>
       </c>
       <c r="J8" s="14">
         <f t="shared" si="3"/>
-        <v>0.22617124394184168</v>
+        <v>0.2245557350565428</v>
       </c>
       <c r="K8" s="15">
         <v>12400</v>
@@ -1000,26 +1030,26 @@
         <v>30.901</v>
       </c>
       <c r="E9" s="13">
-        <f t="shared" si="2"/>
-        <v>140000</v>
+        <f t="shared" ref="E9:E39" si="5">I8</f>
+        <v>139000</v>
       </c>
       <c r="F9" s="13">
         <v>685000</v>
       </c>
       <c r="G9" s="13">
-        <f t="shared" si="0"/>
-        <v>825000</v>
+        <f t="shared" si="2"/>
+        <v>824000</v>
       </c>
       <c r="H9" s="13">
-        <v>433000</v>
+        <v>432000</v>
       </c>
       <c r="I9" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>392000</v>
       </c>
       <c r="J9" s="14">
         <f t="shared" si="3"/>
-        <v>0.90531177829099307</v>
+        <v>0.90740740740740744</v>
       </c>
       <c r="K9" s="15">
         <v>12800</v>
@@ -1053,26 +1083,26 @@
         <v>30.902000000000001</v>
       </c>
       <c r="E10" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>392000</v>
       </c>
       <c r="F10" s="13">
         <v>975000</v>
       </c>
       <c r="G10" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1367000</v>
       </c>
       <c r="H10" s="13">
-        <v>433000</v>
+        <v>432000</v>
       </c>
       <c r="I10" s="13">
-        <f t="shared" si="1"/>
-        <v>934000</v>
+        <f t="shared" si="0"/>
+        <v>935000</v>
       </c>
       <c r="J10" s="14">
         <f t="shared" si="3"/>
-        <v>2.1570438799076213</v>
+        <v>2.1643518518518516</v>
       </c>
       <c r="K10" s="15">
         <v>10300</v>
@@ -1106,26 +1136,26 @@
         <v>30.890999999999998</v>
       </c>
       <c r="E11" s="13">
-        <f t="shared" si="2"/>
-        <v>934000</v>
+        <f t="shared" si="5"/>
+        <v>935000</v>
       </c>
       <c r="F11" s="13">
         <v>440000</v>
       </c>
       <c r="G11" s="13">
-        <f t="shared" si="0"/>
-        <v>1374000</v>
+        <f t="shared" si="2"/>
+        <v>1375000</v>
       </c>
       <c r="H11" s="13">
-        <v>433000</v>
+        <v>432000</v>
       </c>
       <c r="I11" s="13">
-        <f t="shared" si="1"/>
-        <v>941000</v>
+        <f t="shared" si="0"/>
+        <v>943000</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="3"/>
-        <v>2.1732101616628174</v>
+        <v>2.1828703703703702</v>
       </c>
       <c r="K11" s="15">
         <v>10800</v>
@@ -1159,26 +1189,26 @@
         <v>30.9</v>
       </c>
       <c r="E12" s="13">
-        <f t="shared" si="2"/>
-        <v>941000</v>
+        <f t="shared" si="5"/>
+        <v>943000</v>
       </c>
       <c r="F12" s="13">
         <v>410000</v>
       </c>
       <c r="G12" s="13">
-        <f t="shared" si="0"/>
-        <v>1351000</v>
+        <f t="shared" si="2"/>
+        <v>1353000</v>
       </c>
       <c r="H12" s="13">
-        <v>433000</v>
+        <v>432000</v>
       </c>
       <c r="I12" s="13">
-        <f t="shared" si="1"/>
-        <v>918000</v>
+        <f t="shared" si="0"/>
+        <v>921000</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" si="3"/>
-        <v>2.1200923787528869</v>
+        <v>2.1319444444444446</v>
       </c>
       <c r="K12" s="15">
         <v>12700</v>
@@ -1212,26 +1242,26 @@
         <v>30.890999999999998</v>
       </c>
       <c r="E13" s="13">
-        <f t="shared" si="2"/>
-        <v>918000</v>
+        <f t="shared" si="5"/>
+        <v>921000</v>
       </c>
       <c r="F13" s="13">
         <v>290000</v>
       </c>
       <c r="G13" s="13">
-        <f t="shared" si="0"/>
-        <v>1208000</v>
+        <f t="shared" si="2"/>
+        <v>1211000</v>
       </c>
       <c r="H13" s="13">
-        <v>433000</v>
+        <v>432000</v>
       </c>
       <c r="I13" s="13">
-        <f t="shared" si="1"/>
-        <v>775000</v>
+        <f t="shared" si="0"/>
+        <v>779000</v>
       </c>
       <c r="J13" s="14">
         <f t="shared" si="3"/>
-        <v>1.789838337182448</v>
+        <v>1.8032407407407407</v>
       </c>
       <c r="K13" s="15">
         <v>12500</v>
@@ -1265,25 +1295,26 @@
         <v>30.896000000000001</v>
       </c>
       <c r="E14" s="13">
-        <v>778000</v>
+        <f t="shared" si="5"/>
+        <v>779000</v>
       </c>
       <c r="F14" s="13">
         <v>90000</v>
       </c>
       <c r="G14" s="13">
-        <f t="shared" si="0"/>
-        <v>868000</v>
+        <f t="shared" si="2"/>
+        <v>869000</v>
       </c>
       <c r="H14" s="13">
-        <v>433000</v>
+        <v>434000</v>
       </c>
       <c r="I14" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>435000</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="3"/>
-        <v>1.0046189376443417</v>
+        <v>1.0023041474654377</v>
       </c>
       <c r="K14" s="15">
         <v>14900</v>
@@ -1317,20 +1348,21 @@
         <v>30.904</v>
       </c>
       <c r="E15" s="13">
+        <f t="shared" si="5"/>
         <v>435000</v>
       </c>
       <c r="F15" s="13">
         <v>330000</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>765000</v>
       </c>
       <c r="H15" s="13">
         <v>457000</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>308000</v>
       </c>
       <c r="J15" s="14">
@@ -1369,20 +1401,21 @@
         <v>45.442999999999998</v>
       </c>
       <c r="E16" s="13">
+        <f t="shared" si="5"/>
         <v>308000</v>
       </c>
       <c r="F16" s="13">
         <v>750000</v>
       </c>
       <c r="G16" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1058000</v>
       </c>
       <c r="H16" s="13">
         <v>494000</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>564000</v>
       </c>
       <c r="J16" s="14">
@@ -1421,21 +1454,21 @@
         <v>47.817</v>
       </c>
       <c r="E17" s="13">
-        <f>I16</f>
+        <f t="shared" si="5"/>
         <v>564000</v>
       </c>
       <c r="F17" s="13">
         <v>700000</v>
       </c>
       <c r="G17" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1264000</v>
       </c>
       <c r="H17" s="13">
         <v>594000</v>
       </c>
       <c r="I17" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>670000</v>
       </c>
       <c r="J17" s="14">
@@ -1474,21 +1507,21 @@
         <v>47.256999999999998</v>
       </c>
       <c r="E18" s="13">
-        <f>I17</f>
+        <f t="shared" si="5"/>
         <v>670000</v>
       </c>
       <c r="F18" s="13">
         <v>700000</v>
       </c>
       <c r="G18" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1370000</v>
       </c>
       <c r="H18" s="13">
         <v>594000</v>
       </c>
       <c r="I18" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>776000</v>
       </c>
       <c r="J18" s="14">
@@ -1527,21 +1560,21 @@
         <v>47.738</v>
       </c>
       <c r="E19" s="13">
-        <f>I18</f>
+        <f t="shared" si="5"/>
         <v>776000</v>
       </c>
       <c r="F19" s="13">
         <v>640000</v>
       </c>
       <c r="G19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1416000</v>
       </c>
       <c r="H19" s="13">
         <v>619000</v>
       </c>
       <c r="I19" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>797000</v>
       </c>
       <c r="J19" s="14">
@@ -1580,21 +1613,21 @@
         <v>48.183999999999997</v>
       </c>
       <c r="E20" s="13">
-        <f>I19</f>
+        <f t="shared" si="5"/>
         <v>797000</v>
       </c>
       <c r="F20" s="13">
         <v>700000</v>
       </c>
       <c r="G20" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1497000</v>
       </c>
       <c r="H20" s="13">
         <v>619000</v>
       </c>
       <c r="I20" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>878000</v>
       </c>
       <c r="J20" s="14">
@@ -1633,25 +1666,26 @@
         <v>48.183999999999997</v>
       </c>
       <c r="E21" s="13">
+        <f t="shared" si="5"/>
         <v>878000</v>
       </c>
       <c r="F21" s="13">
         <v>800000</v>
       </c>
       <c r="G21" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1678000</v>
       </c>
       <c r="H21" s="13">
-        <v>533000</v>
+        <v>532000</v>
       </c>
       <c r="I21" s="13">
-        <f t="shared" si="1"/>
-        <v>1145000</v>
+        <f t="shared" si="0"/>
+        <v>1146000</v>
       </c>
       <c r="J21" s="14">
         <f t="shared" si="3"/>
-        <v>2.148217636022514</v>
+        <v>2.1541353383458648</v>
       </c>
       <c r="K21" s="15">
         <v>12300</v>
@@ -1685,26 +1719,26 @@
         <v>48.451000000000001</v>
       </c>
       <c r="E22" s="13">
-        <f>I21</f>
-        <v>1145000</v>
+        <f t="shared" si="5"/>
+        <v>1146000</v>
       </c>
       <c r="F22" s="13">
         <v>790000</v>
       </c>
       <c r="G22" s="13">
-        <f t="shared" si="0"/>
-        <v>1935000</v>
+        <f t="shared" si="2"/>
+        <v>1936000</v>
       </c>
       <c r="H22" s="13">
-        <v>533000</v>
+        <v>532000</v>
       </c>
       <c r="I22" s="13">
-        <f t="shared" si="1"/>
-        <v>1402000</v>
+        <f t="shared" si="0"/>
+        <v>1404000</v>
       </c>
       <c r="J22" s="14">
         <f t="shared" si="3"/>
-        <v>2.6303939962476548</v>
+        <v>2.6390977443609023</v>
       </c>
       <c r="K22" s="15">
         <v>11530</v>
@@ -1726,7 +1760,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="22">
-        <v>45931</v>
+        <v>45566</v>
       </c>
       <c r="B23" s="5">
         <v>400</v>
@@ -1737,24 +1771,27 @@
       <c r="D23" s="24">
         <v>48.59</v>
       </c>
-      <c r="E23" s="20">
-        <v>1402000</v>
+      <c r="E23" s="13">
+        <f t="shared" si="5"/>
+        <v>1404000</v>
       </c>
       <c r="F23" s="20">
         <v>720000</v>
       </c>
       <c r="G23" s="20">
-        <v>2122000</v>
+        <f>E23+F23</f>
+        <v>2124000</v>
       </c>
       <c r="H23" s="20">
-        <v>533000</v>
-      </c>
-      <c r="I23" s="20">
-        <v>1589000</v>
+        <v>532000</v>
+      </c>
+      <c r="I23" s="13">
+        <f t="shared" si="0"/>
+        <v>1592000</v>
       </c>
       <c r="J23" s="14">
         <f t="shared" si="3"/>
-        <v>2.9812382739212007</v>
+        <v>2.992481203007519</v>
       </c>
       <c r="K23" s="15">
         <v>11900</v>
@@ -1776,7 +1813,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="22">
-        <v>45985</v>
+        <v>45597</v>
       </c>
       <c r="B24" s="5">
         <v>400</v>
@@ -1787,24 +1824,27 @@
       <c r="D24" s="24">
         <v>49.408999999999999</v>
       </c>
-      <c r="E24" s="20">
-        <v>1589000</v>
+      <c r="E24" s="13">
+        <f t="shared" si="5"/>
+        <v>1592000</v>
       </c>
       <c r="F24" s="20">
         <v>630000</v>
       </c>
       <c r="G24" s="20">
-        <v>2219000</v>
+        <f>E24+F24</f>
+        <v>2222000</v>
       </c>
       <c r="H24" s="20">
-        <v>533000</v>
-      </c>
-      <c r="I24" s="20">
-        <v>1686000</v>
+        <v>532000</v>
+      </c>
+      <c r="I24" s="13">
+        <f>G24-H24</f>
+        <v>1690000</v>
       </c>
       <c r="J24" s="14">
         <f t="shared" si="3"/>
-        <v>3.1632270168855534</v>
+        <v>3.1766917293233083</v>
       </c>
       <c r="K24" s="15">
         <v>12300</v>
@@ -1826,7 +1866,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="22">
-        <v>46015</v>
+        <v>45627</v>
       </c>
       <c r="B25" s="5">
         <v>400</v>
@@ -1837,24 +1877,27 @@
       <c r="D25" s="24">
         <v>50.582000000000001</v>
       </c>
-      <c r="E25" s="20">
-        <v>1686000</v>
+      <c r="E25" s="13">
+        <f t="shared" si="5"/>
+        <v>1690000</v>
       </c>
       <c r="F25" s="20">
         <v>450000</v>
       </c>
       <c r="G25" s="20">
-        <v>2136000</v>
+        <f>E25+F25</f>
+        <v>2140000</v>
       </c>
       <c r="H25" s="20">
-        <v>933000</v>
-      </c>
-      <c r="I25" s="20">
-        <v>1203000</v>
+        <v>932000</v>
+      </c>
+      <c r="I25" s="13">
+        <f>G25-H25</f>
+        <v>1208000</v>
       </c>
       <c r="J25" s="14">
         <f t="shared" si="3"/>
-        <v>1.2893890675241158</v>
+        <v>1.296137339055794</v>
       </c>
       <c r="K25" s="15">
         <v>12400</v>
@@ -1887,24 +1930,27 @@
       <c r="D26" s="24">
         <v>50.44</v>
       </c>
-      <c r="E26" s="20">
-        <v>1205000</v>
+      <c r="E26" s="13">
+        <f t="shared" si="5"/>
+        <v>1208000</v>
       </c>
       <c r="F26" s="20">
-        <v>700000</v>
+        <v>679000</v>
       </c>
       <c r="G26" s="20">
-        <v>1905000</v>
+        <f>E26+F26</f>
+        <v>1887000</v>
       </c>
       <c r="H26" s="20">
-        <v>583000</v>
-      </c>
-      <c r="I26" s="20">
-        <v>1322000</v>
+        <v>584000</v>
+      </c>
+      <c r="I26" s="13">
+        <f>G26-H26</f>
+        <v>1303000</v>
       </c>
       <c r="J26" s="14">
         <f t="shared" si="3"/>
-        <v>2.2675814751286447</v>
+        <v>2.2311643835616439</v>
       </c>
       <c r="K26" s="15">
         <v>13000</v>
@@ -1937,24 +1983,27 @@
       <c r="D27" s="24">
         <v>50.509</v>
       </c>
-      <c r="E27" s="20">
-        <v>1322000</v>
+      <c r="E27" s="13">
+        <f t="shared" si="5"/>
+        <v>1303000</v>
       </c>
       <c r="F27" s="20">
-        <v>1527000</v>
+        <v>786000</v>
       </c>
       <c r="G27" s="20">
-        <v>2849000</v>
+        <f>E27+F27</f>
+        <v>2089000</v>
       </c>
       <c r="H27" s="20">
         <v>507000</v>
       </c>
-      <c r="I27" s="20">
-        <v>2342000</v>
+      <c r="I27" s="13">
+        <f>G27-H27</f>
+        <v>1582000</v>
       </c>
       <c r="J27" s="14">
         <f t="shared" si="3"/>
-        <v>4.6193293885601578</v>
+        <v>3.1203155818540433</v>
       </c>
       <c r="K27" s="15">
         <v>13345</v>
@@ -1987,24 +2036,27 @@
       <c r="D28" s="24">
         <v>50.581000000000003</v>
       </c>
-      <c r="E28" s="20">
-        <v>2343000</v>
+      <c r="E28" s="13">
+        <f t="shared" si="5"/>
+        <v>1582000</v>
       </c>
       <c r="F28" s="20">
-        <v>650000</v>
+        <v>584000</v>
       </c>
       <c r="G28" s="20">
-        <v>2993000</v>
+        <f t="shared" ref="G28:G39" si="6">E28+F28</f>
+        <v>2166000</v>
       </c>
       <c r="H28" s="20">
         <v>644000</v>
       </c>
-      <c r="I28" s="20">
-        <v>2349000</v>
+      <c r="I28" s="13">
+        <f t="shared" si="0"/>
+        <v>1522000</v>
       </c>
       <c r="J28" s="14">
         <f t="shared" si="3"/>
-        <v>3.6475155279503104</v>
+        <v>2.3633540372670807</v>
       </c>
       <c r="K28" s="15">
         <v>13260</v>
@@ -2037,24 +2089,27 @@
       <c r="D29" s="24">
         <v>50.581000000000003</v>
       </c>
-      <c r="E29" s="20">
-        <v>2349000</v>
+      <c r="E29" s="13">
+        <f t="shared" si="5"/>
+        <v>1522000</v>
       </c>
       <c r="F29" s="20">
-        <v>420000</v>
+        <v>398000</v>
       </c>
       <c r="G29" s="20">
-        <v>2769000</v>
+        <f t="shared" si="6"/>
+        <v>1920000</v>
       </c>
       <c r="H29" s="20">
         <v>744000</v>
       </c>
-      <c r="I29" s="20">
-        <v>2025000</v>
+      <c r="I29" s="13">
+        <f t="shared" si="0"/>
+        <v>1176000</v>
       </c>
       <c r="J29" s="14">
         <f t="shared" si="3"/>
-        <v>2.721774193548387</v>
+        <v>1.5806451612903225</v>
       </c>
       <c r="K29" s="15">
         <v>13450</v>
@@ -2087,24 +2142,27 @@
       <c r="D30" s="24">
         <v>50.581000000000003</v>
       </c>
-      <c r="E30" s="20">
-        <v>2025000</v>
+      <c r="E30" s="13">
+        <f t="shared" si="5"/>
+        <v>1176000</v>
       </c>
       <c r="F30" s="20">
-        <v>412000</v>
+        <v>286000</v>
       </c>
       <c r="G30" s="20">
-        <v>2437000</v>
+        <f t="shared" si="6"/>
+        <v>1462000</v>
       </c>
       <c r="H30" s="20">
         <v>744000</v>
       </c>
-      <c r="I30" s="20">
-        <v>1693000</v>
+      <c r="I30" s="13">
+        <f t="shared" si="0"/>
+        <v>718000</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="3"/>
-        <v>2.275537634408602</v>
+        <v>0.96505376344086025</v>
       </c>
       <c r="K30" s="15">
         <v>13460</v>
@@ -2137,24 +2195,27 @@
       <c r="D31" s="24">
         <v>49.933999999999997</v>
       </c>
-      <c r="E31" s="20">
-        <v>1693000</v>
+      <c r="E31" s="13">
+        <f t="shared" si="5"/>
+        <v>718000</v>
       </c>
       <c r="F31" s="20">
-        <v>540000</v>
+        <v>576000</v>
       </c>
       <c r="G31" s="20">
-        <v>2233000</v>
+        <f t="shared" si="6"/>
+        <v>1294000</v>
       </c>
       <c r="H31" s="20">
         <v>769000</v>
       </c>
-      <c r="I31" s="20">
-        <v>1464000</v>
+      <c r="I31" s="13">
+        <f t="shared" si="0"/>
+        <v>525000</v>
       </c>
       <c r="J31" s="14">
         <f t="shared" si="3"/>
-        <v>1.9037711313394019</v>
+        <v>0.68270481144343298</v>
       </c>
       <c r="K31" s="15">
         <v>13475</v>
@@ -2187,24 +2248,27 @@
       <c r="D32" s="24">
         <v>49.250999999999998</v>
       </c>
-      <c r="E32" s="20">
-        <v>1464000</v>
+      <c r="E32" s="13">
+        <f t="shared" si="5"/>
+        <v>525000</v>
       </c>
       <c r="F32" s="20">
-        <v>412000</v>
+        <v>540000</v>
       </c>
       <c r="G32" s="20">
-        <v>1876000</v>
+        <f t="shared" si="6"/>
+        <v>1065000</v>
       </c>
       <c r="H32" s="20">
         <v>769000</v>
       </c>
-      <c r="I32" s="20">
-        <v>1107000</v>
+      <c r="I32" s="13">
+        <f t="shared" si="0"/>
+        <v>296000</v>
       </c>
       <c r="J32" s="14">
         <f t="shared" si="3"/>
-        <v>1.4395318595578674</v>
+        <v>0.38491547464239273</v>
       </c>
       <c r="K32" s="15">
         <v>13680</v>
@@ -2237,24 +2301,27 @@
       <c r="D33" s="24">
         <v>48.484000000000002</v>
       </c>
-      <c r="E33" s="20">
-        <v>1107000</v>
+      <c r="E33" s="13">
+        <f t="shared" si="5"/>
+        <v>296000</v>
       </c>
       <c r="F33" s="20">
-        <v>800000</v>
+        <v>917000</v>
       </c>
       <c r="G33" s="20">
-        <v>1907000</v>
+        <f t="shared" si="6"/>
+        <v>1213000</v>
       </c>
       <c r="H33" s="20">
-        <v>683000</v>
-      </c>
-      <c r="I33" s="20">
-        <v>1224000</v>
+        <v>682000</v>
+      </c>
+      <c r="I33" s="13">
+        <f t="shared" si="0"/>
+        <v>531000</v>
       </c>
       <c r="J33" s="14">
         <f t="shared" si="3"/>
-        <v>1.7920937042459737</v>
+        <v>0.77859237536656889</v>
       </c>
       <c r="K33" s="15">
         <v>12985</v>
@@ -2287,24 +2354,27 @@
       <c r="D34" s="24">
         <v>48.215000000000003</v>
       </c>
-      <c r="E34" s="20">
-        <v>1224000</v>
+      <c r="E34" s="13">
+        <f t="shared" si="5"/>
+        <v>531000</v>
       </c>
       <c r="F34" s="20">
-        <v>790000</v>
+        <v>1078000</v>
       </c>
       <c r="G34" s="20">
-        <v>2014000</v>
+        <f t="shared" si="6"/>
+        <v>1609000</v>
       </c>
       <c r="H34" s="20">
-        <v>683000</v>
-      </c>
-      <c r="I34" s="20">
-        <v>1331000</v>
+        <v>682000</v>
+      </c>
+      <c r="I34" s="13">
+        <f t="shared" si="0"/>
+        <v>927000</v>
       </c>
       <c r="J34" s="14">
         <f t="shared" si="3"/>
-        <v>1.9487554904831625</v>
+        <v>1.3592375366568914</v>
       </c>
       <c r="K34" s="15">
         <v>12325</v>
@@ -2337,27 +2407,27 @@
       <c r="D35" s="24">
         <v>47.5</v>
       </c>
-      <c r="E35" s="20">
-        <f>I34</f>
-        <v>1331000</v>
+      <c r="E35" s="13">
+        <f t="shared" si="5"/>
+        <v>927000</v>
       </c>
       <c r="F35" s="20">
-        <v>720000</v>
+        <v>943000</v>
       </c>
       <c r="G35" s="20">
-        <f>E35+F35</f>
-        <v>2051000</v>
+        <f t="shared" si="6"/>
+        <v>1870000</v>
       </c>
       <c r="H35" s="20">
-        <v>683000</v>
-      </c>
-      <c r="I35" s="20">
-        <f>G35-H35</f>
-        <v>1368000</v>
+        <v>682000</v>
+      </c>
+      <c r="I35" s="13">
+        <f t="shared" si="0"/>
+        <v>1188000</v>
       </c>
       <c r="J35" s="14">
         <f t="shared" si="3"/>
-        <v>2.0029282576866763</v>
+        <v>1.7419354838709677</v>
       </c>
       <c r="K35" s="15">
         <v>12700</v>
@@ -2390,27 +2460,27 @@
       <c r="D36" s="24">
         <v>47.3</v>
       </c>
-      <c r="E36" s="20">
-        <f>I35</f>
-        <v>1368000</v>
+      <c r="E36" s="13">
+        <f t="shared" si="5"/>
+        <v>1188000</v>
       </c>
       <c r="F36" s="20">
-        <v>630000</v>
+        <v>879000</v>
       </c>
       <c r="G36" s="20">
-        <f>E36+F36</f>
-        <v>1998000</v>
+        <f t="shared" si="6"/>
+        <v>2067000</v>
       </c>
       <c r="H36" s="20">
-        <v>683000</v>
-      </c>
-      <c r="I36" s="20">
-        <f>G36-H36</f>
-        <v>1315000</v>
+        <v>682000</v>
+      </c>
+      <c r="I36" s="13">
+        <f t="shared" si="0"/>
+        <v>1385000</v>
       </c>
       <c r="J36" s="14">
         <f t="shared" si="3"/>
-        <v>1.9253294289897511</v>
+        <v>2.030791788856305</v>
       </c>
       <c r="K36" s="15">
         <v>12300</v>
@@ -2443,27 +2513,27 @@
       <c r="D37" s="24">
         <v>47.4</v>
       </c>
-      <c r="E37" s="20">
-        <f>I36</f>
-        <v>1315000</v>
+      <c r="E37" s="13">
+        <f t="shared" si="5"/>
+        <v>1385000</v>
       </c>
       <c r="F37" s="20">
-        <v>700000</v>
+        <v>534000</v>
       </c>
       <c r="G37" s="20">
-        <f>E37+F37</f>
-        <v>2015000</v>
+        <f t="shared" si="6"/>
+        <v>1919000</v>
       </c>
       <c r="H37" s="20">
-        <v>600000</v>
-      </c>
-      <c r="I37" s="20">
-        <f>G37-H37</f>
-        <v>1415000</v>
+        <v>582000</v>
+      </c>
+      <c r="I37" s="13">
+        <f t="shared" si="0"/>
+        <v>1337000</v>
       </c>
       <c r="J37" s="14">
         <f t="shared" si="3"/>
-        <v>2.3583333333333334</v>
+        <v>2.297250859106529</v>
       </c>
       <c r="K37" s="15">
         <v>12300</v>
@@ -2498,27 +2568,27 @@
       <c r="D38" s="24">
         <v>47.25</v>
       </c>
-      <c r="E38" s="20">
-        <f>I37</f>
-        <v>1415000</v>
+      <c r="E38" s="13">
+        <f t="shared" si="5"/>
+        <v>1337000</v>
       </c>
       <c r="F38" s="20">
-        <v>400000</v>
+        <v>466000</v>
       </c>
       <c r="G38" s="20">
-        <f>E38+F38</f>
-        <v>1815000</v>
+        <f t="shared" si="6"/>
+        <v>1803000</v>
       </c>
       <c r="H38" s="20">
-        <v>600000</v>
-      </c>
-      <c r="I38" s="20">
-        <f>G38-H38</f>
-        <v>1215000</v>
+        <v>584000</v>
+      </c>
+      <c r="I38" s="13">
+        <f t="shared" si="0"/>
+        <v>1219000</v>
       </c>
       <c r="J38" s="14">
         <f t="shared" si="3"/>
-        <v>2.0249999999999999</v>
+        <v>2.0873287671232879</v>
       </c>
       <c r="K38" s="15">
         <v>0</v>
@@ -2546,26 +2616,27 @@
       <c r="D39" s="24">
         <v>47.148400000000002</v>
       </c>
-      <c r="E39" s="20">
-        <v>1600000</v>
+      <c r="E39" s="13">
+        <f t="shared" si="5"/>
+        <v>1219000</v>
       </c>
       <c r="F39" s="20">
-        <v>700000</v>
+        <v>730000</v>
       </c>
       <c r="G39" s="20">
-        <f>E39+F39</f>
-        <v>2300000</v>
+        <f t="shared" si="6"/>
+        <v>1949000</v>
       </c>
       <c r="H39" s="20">
         <v>657000</v>
       </c>
-      <c r="I39" s="20">
-        <f>G39-H39</f>
-        <v>1643000</v>
+      <c r="I39" s="13">
+        <f t="shared" si="0"/>
+        <v>1292000</v>
       </c>
       <c r="J39" s="14">
         <f t="shared" si="3"/>
-        <v>2.5007610350076104</v>
+        <v>1.9665144596651445</v>
       </c>
       <c r="K39" s="15">
         <v>0</v>
@@ -2584,19 +2655,37 @@
       <c r="A40" s="22">
         <v>46082</v>
       </c>
-      <c r="B40" s="3"/>
+      <c r="B40" s="5">
+        <v>429</v>
+      </c>
       <c r="C40" s="1">
         <v>564</v>
       </c>
       <c r="D40" s="24">
         <v>50</v>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
+      <c r="E40" s="20">
+        <f>I39</f>
+        <v>1292000</v>
+      </c>
+      <c r="F40" s="20">
+        <v>1000000</v>
+      </c>
+      <c r="G40" s="20">
+        <f>E40+F40</f>
+        <v>2292000</v>
+      </c>
+      <c r="H40" s="20">
+        <v>644000</v>
+      </c>
+      <c r="I40" s="20">
+        <f t="shared" si="0"/>
+        <v>1648000</v>
+      </c>
+      <c r="J40" s="3">
+        <f t="shared" si="3"/>
+        <v>2.5590062111801242</v>
+      </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
@@ -2607,19 +2696,37 @@
       <c r="A41" s="22">
         <v>46113</v>
       </c>
-      <c r="B41" s="3"/>
+      <c r="B41" s="5">
+        <v>429</v>
+      </c>
       <c r="C41" s="1">
         <v>571</v>
       </c>
       <c r="D41" s="24">
         <v>53</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
+      <c r="E41" s="20">
+        <f t="shared" ref="E41:E42" si="7">I40</f>
+        <v>1648000</v>
+      </c>
+      <c r="F41" s="20">
+        <v>700000</v>
+      </c>
+      <c r="G41" s="20">
+        <f>E41+F41</f>
+        <v>2348000</v>
+      </c>
+      <c r="H41" s="20">
+        <v>744000</v>
+      </c>
+      <c r="I41" s="20">
+        <f t="shared" si="0"/>
+        <v>1604000</v>
+      </c>
+      <c r="J41" s="3">
+        <f t="shared" si="3"/>
+        <v>2.1559139784946235</v>
+      </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -2630,19 +2737,37 @@
       <c r="A42" s="22">
         <v>46143</v>
       </c>
-      <c r="B42" s="3"/>
+      <c r="B42" s="5">
+        <v>429</v>
+      </c>
       <c r="C42" s="1">
         <v>636</v>
       </c>
       <c r="D42" s="24">
         <v>52</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
+      <c r="E42" s="20">
+        <f t="shared" si="7"/>
+        <v>1604000</v>
+      </c>
+      <c r="F42" s="20">
+        <v>700000</v>
+      </c>
+      <c r="G42" s="20">
+        <f>E42+F42</f>
+        <v>2304000</v>
+      </c>
+      <c r="H42" s="20">
+        <v>744000</v>
+      </c>
+      <c r="I42" s="20">
+        <f t="shared" si="0"/>
+        <v>1560000</v>
+      </c>
+      <c r="J42" s="3">
+        <f t="shared" si="3"/>
+        <v>2.096774193548387</v>
+      </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -2653,7 +2778,6 @@
       <c r="A43" s="21"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="1"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2670,7 +2794,6 @@
       <c r="A44" s="21"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="1"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -2687,7 +2810,6 @@
       <c r="A45" s="21"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="1"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -2704,7 +2826,6 @@
       <c r="A46" s="21"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="1"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -2721,7 +2842,6 @@
       <c r="A47" s="21"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="1"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -2738,7 +2858,6 @@
       <c r="A48" s="21"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="1"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -2755,7 +2874,6 @@
       <c r="A49" s="21"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="1"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2772,7 +2890,6 @@
       <c r="A50" s="21"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="1"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -2789,7 +2906,6 @@
       <c r="A51" s="21"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="1"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -2806,7 +2922,6 @@
       <c r="A52" s="21"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="1"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -2823,7 +2938,6 @@
       <c r="A53" s="21"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="1"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -2840,7 +2954,6 @@
       <c r="A54" s="21"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="1"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -2857,7 +2970,6 @@
       <c r="A55" s="21"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="1"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -2874,7 +2986,6 @@
       <c r="A56" s="21"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="1"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
@@ -2891,7 +3002,6 @@
       <c r="A57" s="21"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="1"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -2908,7 +3018,6 @@
       <c r="A58" s="21"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="1"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
@@ -2925,7 +3034,6 @@
       <c r="A59" s="21"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="1"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
@@ -2942,7 +3050,6 @@
       <c r="A60" s="21"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="1"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
@@ -2959,7 +3066,6 @@
       <c r="A61" s="21"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="1"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
@@ -2976,7 +3082,6 @@
       <c r="A62" s="21"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="1"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
@@ -2993,7 +3098,6 @@
       <c r="A63" s="21"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="1"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
@@ -3010,7 +3114,6 @@
       <c r="A64" s="21"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="1"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
@@ -3027,7 +3130,6 @@
       <c r="A65" s="21"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="1"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
@@ -3044,7 +3146,6 @@
       <c r="A66" s="21"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="1"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -3061,7 +3162,6 @@
       <c r="A67" s="21"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="1"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -3078,7 +3178,6 @@
       <c r="A68" s="21"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="1"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -3095,7 +3194,6 @@
       <c r="A69" s="21"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="1"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -3112,7 +3210,6 @@
       <c r="A70" s="21"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="1"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -3129,7 +3226,6 @@
       <c r="A71" s="21"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="1"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -3146,7 +3242,6 @@
       <c r="A72" s="21"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="1"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -3163,7 +3258,6 @@
       <c r="A73" s="21"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="1"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
@@ -3180,7 +3274,6 @@
       <c r="A74" s="21"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="1"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
@@ -3197,7 +3290,6 @@
       <c r="A75" s="21"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="1"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
@@ -3214,7 +3306,6 @@
       <c r="A76" s="21"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="1"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
@@ -3231,7 +3322,6 @@
       <c r="A77" s="21"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="1"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
@@ -3248,7 +3338,6 @@
       <c r="A78" s="21"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="1"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -3265,7 +3354,6 @@
       <c r="A79" s="21"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="1"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -3282,7 +3370,6 @@
       <c r="A80" s="21"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="1"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -3299,7 +3386,6 @@
       <c r="A81" s="21"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="1"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>

--- a/Wheat.xlsx
+++ b/Wheat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adm-my.sharepoint.com/personal/zeina_sherif_adm-medsofts_com/Documents/Documents/Commodity/Wheat/Local/Model Monthly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="449" documentId="11_AD4D80C4656A4B7AC02E743F331E4E205ADEDD8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7B3BEB-1D5A-4803-B5EC-600F9DDEE3B5}"/>
+  <xr:revisionPtr revIDLastSave="461" documentId="11_AD4D80C4656A4B7AC02E743F331E4E205ADEDD8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8822A845-57BF-47DF-842B-2E61AB322F5E}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="2810" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -310,10 +310,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -673,7 +669,7 @@
         <v>434000</v>
       </c>
       <c r="I2" s="13">
-        <f t="shared" ref="I2:I42" si="0">G2-H2</f>
+        <f t="shared" ref="I2:I43" si="0">G2-H2</f>
         <v>346000</v>
       </c>
       <c r="J2" s="14">
@@ -730,7 +726,7 @@
         <v>319000</v>
       </c>
       <c r="J3" s="14">
-        <f t="shared" ref="J3:J42" si="3">I3/H3</f>
+        <f t="shared" ref="J3:J43" si="3">I3/H3</f>
         <v>0.69803063457330417</v>
       </c>
       <c r="K3" s="15">
@@ -2706,7 +2702,7 @@
         <v>53</v>
       </c>
       <c r="E41" s="20">
-        <f t="shared" ref="E41:E42" si="7">I40</f>
+        <f t="shared" ref="E41:E43" si="7">I40</f>
         <v>1648000</v>
       </c>
       <c r="F41" s="20">
@@ -2775,15 +2771,40 @@
       <c r="O42" s="3"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A43" s="21"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
+      <c r="A43" s="22">
+        <v>46174</v>
+      </c>
+      <c r="B43" s="5">
+        <v>429</v>
+      </c>
+      <c r="C43" s="1">
+        <v>600</v>
+      </c>
+      <c r="D43" s="24">
+        <v>50</v>
+      </c>
+      <c r="E43" s="20">
+        <f t="shared" si="7"/>
+        <v>1560000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>700000</v>
+      </c>
+      <c r="G43" s="3">
+        <f>E43+F43</f>
+        <v>2260000</v>
+      </c>
+      <c r="H43" s="3">
+        <v>769000</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="0"/>
+        <v>1491000</v>
+      </c>
+      <c r="J43" s="3">
+        <f t="shared" si="3"/>
+        <v>1.9388816644993498</v>
+      </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>

--- a/Wheat.xlsx
+++ b/Wheat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adm-my.sharepoint.com/personal/zeina_sherif_adm-medsofts_com/Documents/Documents/Commodity/Wheat/Local/Model Monthly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="461" documentId="11_AD4D80C4656A4B7AC02E743F331E4E205ADEDD8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8822A845-57BF-47DF-842B-2E61AB322F5E}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="11_AD4D80C4656A4B7AC02E743F331E4E205ADEDD8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1006B82-62F4-425F-AF24-E74077493C90}"/>
   <bookViews>
-    <workbookView xWindow="2380" yWindow="2810" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SnD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">12.5% Replacement </t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>Difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -308,6 +305,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2587,14 +2588,16 @@
         <v>2.0873287671232879</v>
       </c>
       <c r="K38" s="15">
-        <v>0</v>
-      </c>
-      <c r="L38" s="16"/>
+        <v>12350</v>
+      </c>
+      <c r="L38" s="16">
+        <v>248</v>
+      </c>
       <c r="M38" s="15">
-        <v>12637.280174752979</v>
-      </c>
-      <c r="N38" s="16" t="s">
-        <v>15</v>
+        <v>12450</v>
+      </c>
+      <c r="N38" s="16">
+        <v>252</v>
       </c>
       <c r="O38" s="10"/>
       <c r="P38" s="2"/>
@@ -2635,14 +2638,16 @@
         <v>1.9665144596651445</v>
       </c>
       <c r="K39" s="15">
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="L39" s="16">
         <v>250</v>
       </c>
-      <c r="M39" s="15"/>
+      <c r="M39" s="15">
+        <v>12500</v>
+      </c>
       <c r="N39" s="16">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O39" s="10"/>
       <c r="P39" s="2"/>
@@ -2682,10 +2687,18 @@
         <f t="shared" si="3"/>
         <v>2.5590062111801242</v>
       </c>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
+      <c r="K40" s="15">
+        <v>13300</v>
+      </c>
+      <c r="L40" s="16">
+        <v>258</v>
+      </c>
+      <c r="M40" s="15">
+        <v>13400</v>
+      </c>
+      <c r="N40" s="16">
+        <v>260</v>
+      </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
@@ -2723,10 +2736,18 @@
         <f t="shared" si="3"/>
         <v>2.1559139784946235</v>
       </c>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
+      <c r="K41" s="15">
+        <v>13900</v>
+      </c>
+      <c r="L41" s="16">
+        <v>263</v>
+      </c>
+      <c r="M41" s="15">
+        <v>14000</v>
+      </c>
+      <c r="N41" s="16">
+        <v>265</v>
+      </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
@@ -2764,10 +2785,18 @@
         <f t="shared" si="3"/>
         <v>2.096774193548387</v>
       </c>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
+      <c r="K42" s="15">
+        <v>13450</v>
+      </c>
+      <c r="L42" s="16">
+        <v>258</v>
+      </c>
+      <c r="M42" s="15">
+        <v>13650</v>
+      </c>
+      <c r="N42" s="16">
+        <v>260</v>
+      </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
@@ -2806,9 +2835,13 @@
         <v>1.9388816644993498</v>
       </c>
       <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+      <c r="L43" s="16">
+        <v>258</v>
+      </c>
       <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
+      <c r="N43" s="16">
+        <v>260</v>
+      </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
